--- a/output/pdf_financials_xlsx/LULU.xlsx
+++ b/output/pdf_financials_xlsx/LULU.xlsx
@@ -1221,10 +1221,10 @@
         </is>
       </c>
       <c r="C48" s="3" t="n">
-        <v>251.459</v>
+        <v>433.712</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>211.62</v>
+        <v>564.0890000000001</v>
       </c>
     </row>
     <row r="49">
@@ -2945,7 +2945,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>OtherCurrentAssets</t>
+          <t>CurrentAssets</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -5324,7 +5324,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>SharesOutstanding</t>
+          <t>BasicAverageShares</t>
         </is>
       </c>
       <c r="E85" s="5" t="n">
@@ -5355,7 +5355,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>SharesOutstanding</t>
+          <t>BasicAverageShares</t>
         </is>
       </c>
       <c r="E86" s="5" t="n">

--- a/output/pdf_financials_xlsx/LULU.xlsx
+++ b/output/pdf_financials_xlsx/LULU.xlsx
@@ -877,13 +877,13 @@
         </is>
       </c>
       <c r="B28" s="3" t="n">
-        <v>379.384</v>
+        <v>5.01</v>
       </c>
       <c r="C28" s="3" t="n">
-        <v>446.524</v>
+        <v>2.735</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>496.228</v>
+        <v>6.961</v>
       </c>
     </row>
     <row r="29">
@@ -893,13 +893,13 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>2555.119</v>
+        <v>2180.745</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>3022.601</v>
+        <v>2578.812</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>2735.195</v>
+        <v>2245.928</v>
       </c>
     </row>
     <row r="30">
@@ -909,13 +909,13 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>26.56248213223487</v>
+        <v>22.67056841480203</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>28.5470818915453</v>
+        <v>24.35569807159454</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>24.6356258894313</v>
+        <v>20.22884729702952</v>
       </c>
     </row>
     <row r="31">
@@ -4968,7 +4968,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E73" s="5" t="n">

--- a/output/pdf_financials_xlsx/LULU.xlsx
+++ b/output/pdf_financials_xlsx/LULU.xlsx
@@ -2215,13 +2215,13 @@
         </is>
       </c>
       <c r="B103" s="3" t="n">
-        <v>0</v>
+        <v>40.587</v>
       </c>
       <c r="C103" s="3" t="n">
-        <v>0</v>
+        <v>-71.789</v>
       </c>
       <c r="D103" s="3" t="n">
-        <v>0</v>
+        <v>47.779</v>
       </c>
     </row>
     <row r="104">
@@ -2263,13 +2263,13 @@
         </is>
       </c>
       <c r="B106" s="3" t="n">
-        <v>250.531</v>
+        <v>291.118</v>
       </c>
       <c r="C106" s="3" t="n">
-        <v>-211.503</v>
+        <v>-283.292</v>
       </c>
       <c r="D106" s="3" t="n">
-        <v>-208.609</v>
+        <v>-160.83</v>
       </c>
     </row>
     <row r="107">
@@ -4119,7 +4119,11 @@
           <t>Prepaid expenses and other current assets</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr"/>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>ChangeInPrepaidAssets</t>
+        </is>
+      </c>
       <c r="E44" s="5" t="n">
         <v>40.587</v>
       </c>
